--- a/examples/raw_data.xlsx
+++ b/examples/raw_data.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lizi/Desktop/biimperative/incompleteIMP/src/IMP/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lizi/Desktop/biimperative/incompleteIMP/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69ACDA4D-6592-214D-8400-443875504670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48571BB-BCEC-7B44-B523-18ABF04EBD5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3800" yWindow="500" windowWidth="21800" windowHeight="14920" activeTab="1" xr2:uid="{4A7AD6E8-1D24-084F-B0AF-95E7CADD8777}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Fwd&amp;Bwd" sheetId="1" r:id="rId1"/>
+    <sheet name="Fill-and-Resume" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="32">
   <si>
     <t>Example</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -142,7 +142,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Avg</t>
+    <t>DP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The First Experiment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Second Experiment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Third Experiment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -150,6 +170,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="12"/>
@@ -189,12 +212,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -902,30 +931,30 @@
         <v>2</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H10">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I10">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J10">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L10">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="M10">
         <f t="shared" si="1"/>
-        <v>23.8</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1155,433 +1184,980 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17BC25D-86D6-8249-AF42-73AC4288A3EC}">
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AB27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
-      <c r="B1" s="1">
-        <v>1</v>
-      </c>
+    <row r="1" spans="1:28">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1">
-        <v>2</v>
-      </c>
+      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="X1" s="1" t="s">
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+    </row>
+    <row r="2" spans="1:28">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-    </row>
-    <row r="2" spans="1:30">
-      <c r="A2" t="s">
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:28">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>15</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="A8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:28">
+      <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" t="s">
+    </row>
+    <row r="10" spans="1:28">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>7</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>3</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:28">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
+      <c r="G16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M2" t="s">
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N2" t="s">
+      <c r="K16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O2" t="s">
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="s">
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" t="s">
+        <v>28</v>
+      </c>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>9</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>6</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20">
+        <v>2</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R2" t="s">
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="S2" t="s">
+      <c r="G23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="T2" t="s">
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="U2" t="s">
+      <c r="K23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V2" t="s">
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="X2" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30">
-      <c r="A3" t="s">
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" t="s">
+        <v>28</v>
+      </c>
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>16</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>11</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>3</v>
-      </c>
-      <c r="T3">
-        <v>2</v>
-      </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
-      <c r="V3">
-        <v>1</v>
-      </c>
-      <c r="X3">
-        <f>AVERAGE(P3,I3,B3)</f>
-        <v>3</v>
-      </c>
-      <c r="Y3">
-        <f>AVERAGE(Q3,J3,C3)</f>
-        <v>12.666666666666666</v>
-      </c>
-      <c r="Z3">
-        <f t="shared" ref="Z3:AD3" si="0">AVERAGE(R3,K3,D3)</f>
+      <c r="B25" s="3">
+        <f>AVERAGE(B4,B11,B18)</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="C25" s="3">
+        <f>AVERAGE(C4,C11,C18)</f>
+        <v>7.666666666666667</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" ref="C25:N25" si="0">AVERAGE(D4,D11,D18)</f>
         <v>1.6666666666666667</v>
       </c>
-      <c r="AA3">
+      <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="AB3">
+        <v>11.333333333333334</v>
+      </c>
+      <c r="F25" s="3">
         <f t="shared" si="0"/>
         <v>1.6666666666666667</v>
       </c>
-      <c r="AC3">
+      <c r="G25" s="3">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AD3">
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="J25" s="3">
         <f t="shared" si="0"/>
         <v>1.3333333333333333</v>
       </c>
-    </row>
-    <row r="4" spans="1:30">
-      <c r="A4" t="s">
+      <c r="K25" s="3">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L25" s="3">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M25" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N25" s="3">
+        <f t="shared" si="0"/>
+        <v>1.6666666666666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>2</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="V4">
-        <v>1</v>
-      </c>
-      <c r="X4">
-        <f t="shared" ref="X4:X5" si="1">AVERAGE(P4,I4,B4)</f>
+      <c r="B26" s="3">
+        <f t="shared" ref="B26:N27" si="1">AVERAGE(B5,B12,B19)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C26" s="3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="D26" s="3">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J26" s="3">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="K26" s="3">
+        <f t="shared" si="1"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="Y4">
-        <f t="shared" ref="Y4:Y5" si="2">AVERAGE(Q4,J4,C4)</f>
+      <c r="L26" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="N26" s="3">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="3">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="C27" s="3">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D27" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" si="1"/>
         <v>1.6666666666666667</v>
       </c>
-      <c r="Z4">
-        <f t="shared" ref="Z4:Z5" si="3">AVERAGE(R4,K4,D4)</f>
-        <v>1</v>
-      </c>
-      <c r="AA4">
-        <f t="shared" ref="AA4:AA5" si="4">AVERAGE(S4,L4,E4)</f>
-        <v>2</v>
-      </c>
-      <c r="AB4">
-        <f t="shared" ref="AB4:AB5" si="5">AVERAGE(T4,M4,F4)</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AC4">
-        <f t="shared" ref="AC4:AC5" si="6">AVERAGE(U4,N4,G4)</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AD4">
-        <f t="shared" ref="AD4:AD5" si="7">AVERAGE(V4,O4,H4)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
+      <c r="G27" s="3">
+        <f t="shared" si="1"/>
+        <v>5.666666666666667</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>3</v>
-      </c>
-      <c r="P5">
-        <v>3</v>
-      </c>
-      <c r="Q5">
-        <v>4</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>8</v>
-      </c>
-      <c r="T5">
-        <v>3</v>
-      </c>
-      <c r="U5">
-        <v>2</v>
-      </c>
-      <c r="V5">
-        <v>2</v>
-      </c>
-      <c r="X5">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="Y5">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="Z5">
-        <f t="shared" si="3"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="AA5">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="AB5">
-        <f t="shared" si="5"/>
-        <v>2.6666666666666665</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" si="6"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" si="7"/>
-        <v>2.6666666666666665</v>
+      <c r="J27" s="3">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="K27" s="3">
+        <f t="shared" si="1"/>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="L27" s="3">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M27" s="3">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="N27" s="3">
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="X1:AD1"/>
+  <mergeCells count="37">
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="A15:N15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="O12:Z12"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="A8:N8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
